--- a/data/ES_20260526_V1_Claude.xlsx
+++ b/data/ES_20260526_V1_Claude.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\20260905-ifr\20260524-sheet-analysis\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\20260905-ifr\20260509-plausibility-analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_504D05E3A2B9A630AB3F1535932C1A38C5E42AC9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="19695" windowHeight="13740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="19695" windowHeight="13740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overview" sheetId="1" r:id="rId1"/>
@@ -5731,20 +5731,22 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
@@ -5753,15 +5755,13 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="5" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5801,13 +5801,13 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6953,20 +6953,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="172" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
+      <c r="A1" s="182" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="178"/>
+      <c r="L1" s="178"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1"/>
@@ -7081,14 +7081,14 @@
       <c r="C5" s="189" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="173"/>
-      <c r="E5" s="173"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="173"/>
-      <c r="I5" s="173"/>
-      <c r="J5" s="173"/>
-      <c r="K5" s="173"/>
+      <c r="D5" s="178"/>
+      <c r="E5" s="178"/>
+      <c r="F5" s="178"/>
+      <c r="G5" s="178"/>
+      <c r="H5" s="178"/>
+      <c r="I5" s="178"/>
+      <c r="J5" s="178"/>
+      <c r="K5" s="178"/>
       <c r="L5" s="13"/>
     </row>
     <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7097,14 +7097,14 @@
       <c r="C6" s="188" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="173"/>
-      <c r="E6" s="173"/>
-      <c r="F6" s="173"/>
-      <c r="G6" s="173"/>
-      <c r="H6" s="173"/>
-      <c r="I6" s="173"/>
-      <c r="J6" s="173"/>
-      <c r="K6" s="173"/>
+      <c r="D6" s="178"/>
+      <c r="E6" s="178"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="178"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="178"/>
+      <c r="J6" s="178"/>
+      <c r="K6" s="178"/>
       <c r="L6" s="13"/>
     </row>
     <row r="7" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7113,14 +7113,14 @@
       <c r="C7" s="187" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="173"/>
-      <c r="E7" s="173"/>
-      <c r="F7" s="173"/>
-      <c r="G7" s="173"/>
-      <c r="H7" s="173"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="173"/>
-      <c r="K7" s="173"/>
+      <c r="D7" s="178"/>
+      <c r="E7" s="178"/>
+      <c r="F7" s="178"/>
+      <c r="G7" s="178"/>
+      <c r="H7" s="178"/>
+      <c r="I7" s="178"/>
+      <c r="J7" s="178"/>
+      <c r="K7" s="178"/>
       <c r="L7" s="13"/>
     </row>
     <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7158,15 +7158,15 @@
       <c r="B10" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="176"/>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="175"/>
-      <c r="I10" s="175"/>
-      <c r="J10" s="175"/>
-      <c r="K10" s="175"/>
+      <c r="C10" s="184"/>
+      <c r="D10" s="173"/>
+      <c r="E10" s="173"/>
+      <c r="F10" s="173"/>
+      <c r="G10" s="173"/>
+      <c r="H10" s="173"/>
+      <c r="I10" s="173"/>
+      <c r="J10" s="173"/>
+      <c r="K10" s="173"/>
       <c r="L10" s="22"/>
     </row>
     <row r="11" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7176,17 +7176,17 @@
       <c r="B11" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="174" t="s">
+      <c r="C11" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="175"/>
-      <c r="E11" s="175"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="175"/>
-      <c r="I11" s="175"/>
-      <c r="J11" s="175"/>
-      <c r="K11" s="175"/>
+      <c r="D11" s="173"/>
+      <c r="E11" s="173"/>
+      <c r="F11" s="173"/>
+      <c r="G11" s="173"/>
+      <c r="H11" s="173"/>
+      <c r="I11" s="173"/>
+      <c r="J11" s="173"/>
+      <c r="K11" s="173"/>
       <c r="L11" s="13"/>
     </row>
     <row r="12" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7196,17 +7196,17 @@
       <c r="B12" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="174" t="s">
+      <c r="C12" s="183" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="175"/>
-      <c r="E12" s="175"/>
-      <c r="F12" s="175"/>
-      <c r="G12" s="175"/>
-      <c r="H12" s="175"/>
-      <c r="I12" s="175"/>
-      <c r="J12" s="175"/>
-      <c r="K12" s="175"/>
+      <c r="D12" s="173"/>
+      <c r="E12" s="173"/>
+      <c r="F12" s="173"/>
+      <c r="G12" s="173"/>
+      <c r="H12" s="173"/>
+      <c r="I12" s="173"/>
+      <c r="J12" s="173"/>
+      <c r="K12" s="173"/>
       <c r="L12" s="13"/>
     </row>
     <row r="13" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7216,17 +7216,17 @@
       <c r="B13" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="174" t="s">
+      <c r="C13" s="183" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="175"/>
-      <c r="E13" s="175"/>
-      <c r="F13" s="175"/>
-      <c r="G13" s="175"/>
-      <c r="H13" s="175"/>
-      <c r="I13" s="175"/>
-      <c r="J13" s="175"/>
-      <c r="K13" s="175"/>
+      <c r="D13" s="173"/>
+      <c r="E13" s="173"/>
+      <c r="F13" s="173"/>
+      <c r="G13" s="173"/>
+      <c r="H13" s="173"/>
+      <c r="I13" s="173"/>
+      <c r="J13" s="173"/>
+      <c r="K13" s="173"/>
       <c r="L13" s="13"/>
     </row>
     <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7248,17 +7248,17 @@
       <c r="B15" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="177" t="s">
+      <c r="C15" s="176" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="175"/>
-      <c r="E15" s="175"/>
-      <c r="F15" s="175"/>
-      <c r="G15" s="175"/>
-      <c r="H15" s="175"/>
-      <c r="I15" s="175"/>
-      <c r="J15" s="175"/>
-      <c r="K15" s="175"/>
+      <c r="D15" s="173"/>
+      <c r="E15" s="173"/>
+      <c r="F15" s="173"/>
+      <c r="G15" s="173"/>
+      <c r="H15" s="173"/>
+      <c r="I15" s="173"/>
+      <c r="J15" s="173"/>
+      <c r="K15" s="173"/>
       <c r="L15" s="22"/>
     </row>
     <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7288,11 +7288,11 @@
         <f t="array" ref="D17">C34</f>
         <v>0.24526247584636998</v>
       </c>
-      <c r="E17" s="178" t="s">
+      <c r="E17" s="177" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="173"/>
-      <c r="G17" s="173"/>
+      <c r="F17" s="178"/>
+      <c r="G17" s="178"/>
       <c r="H17" s="29">
         <f t="array" ref="H17">population!H109</f>
         <v>37078357.906269647</v>
@@ -7377,12 +7377,12 @@
         <v>45</v>
       </c>
       <c r="C21" s="12"/>
-      <c r="D21" s="178" t="s">
+      <c r="D21" s="177" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="173"/>
-      <c r="F21" s="173"/>
-      <c r="G21" s="173"/>
+      <c r="E21" s="178"/>
+      <c r="F21" s="178"/>
+      <c r="G21" s="178"/>
       <c r="H21" s="29">
         <f t="array" ref="H21">IF(ISNUMBER(H20),H20,H19)</f>
         <v>207604.28904595057</v>
@@ -7452,11 +7452,11 @@
         <f t="array" ref="D24">C24/C17</f>
         <v>1.3666742306962401E-2</v>
       </c>
-      <c r="E24" s="178" t="s">
+      <c r="E24" s="177" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="173"/>
-      <c r="G24" s="173"/>
+      <c r="F24" s="178"/>
+      <c r="G24" s="178"/>
       <c r="H24" s="29">
         <f t="array" ref="H24">H21+H22+H23</f>
         <v>-220741.25250882262</v>
@@ -7495,9 +7495,9 @@
       <c r="D26" s="181" t="s">
         <v>52</v>
       </c>
-      <c r="E26" s="173"/>
-      <c r="F26" s="173"/>
-      <c r="G26" s="173"/>
+      <c r="E26" s="178"/>
+      <c r="F26" s="178"/>
+      <c r="G26" s="178"/>
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
@@ -7535,9 +7535,9 @@
       <c r="D28" s="181" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="173"/>
-      <c r="F28" s="173"/>
-      <c r="G28" s="173"/>
+      <c r="E28" s="178"/>
+      <c r="F28" s="178"/>
+      <c r="G28" s="178"/>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
@@ -7582,17 +7582,17 @@
       <c r="B31" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="177" t="s">
+      <c r="C31" s="176" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="175"/>
-      <c r="E31" s="175"/>
-      <c r="F31" s="175"/>
-      <c r="G31" s="175"/>
-      <c r="H31" s="175"/>
-      <c r="I31" s="175"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="175"/>
+      <c r="D31" s="173"/>
+      <c r="E31" s="173"/>
+      <c r="F31" s="173"/>
+      <c r="G31" s="173"/>
+      <c r="H31" s="173"/>
+      <c r="I31" s="173"/>
+      <c r="J31" s="173"/>
+      <c r="K31" s="173"/>
       <c r="L31" s="22"/>
     </row>
     <row r="32" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7661,9 +7661,9 @@
       <c r="D35" s="181" t="s">
         <v>63</v>
       </c>
-      <c r="E35" s="173"/>
-      <c r="F35" s="173"/>
-      <c r="G35" s="173"/>
+      <c r="E35" s="178"/>
+      <c r="F35" s="178"/>
+      <c r="G35" s="178"/>
       <c r="H35" s="36">
         <f t="array" ref="H35">births!H11/births!D9*1000000</f>
         <v>28923.667275300963</v>
@@ -7688,9 +7688,9 @@
       <c r="D36" s="181" t="s">
         <v>65</v>
       </c>
-      <c r="E36" s="173"/>
-      <c r="F36" s="173"/>
-      <c r="G36" s="173"/>
+      <c r="E36" s="178"/>
+      <c r="F36" s="178"/>
+      <c r="G36" s="178"/>
       <c r="H36" s="27">
         <f t="array" ref="H36">births!H11/population!H109*1000000</f>
         <v>5599.0691273533012</v>
@@ -7715,9 +7715,9 @@
       <c r="D37" s="181" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="173"/>
-      <c r="F37" s="173"/>
-      <c r="G37" s="173"/>
+      <c r="E37" s="178"/>
+      <c r="F37" s="178"/>
+      <c r="G37" s="178"/>
       <c r="H37" s="27">
         <f t="array" ref="H37">deaths!H$107/population!H$109*1000000</f>
         <v>10730.794566484696</v>
@@ -7877,17 +7877,17 @@
       <c r="B47" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C47" s="177" t="s">
+      <c r="C47" s="176" t="s">
         <v>71</v>
       </c>
-      <c r="D47" s="175"/>
-      <c r="E47" s="175"/>
-      <c r="F47" s="175"/>
-      <c r="G47" s="175"/>
-      <c r="H47" s="175"/>
-      <c r="I47" s="175"/>
-      <c r="J47" s="175"/>
-      <c r="K47" s="175"/>
+      <c r="D47" s="173"/>
+      <c r="E47" s="173"/>
+      <c r="F47" s="173"/>
+      <c r="G47" s="173"/>
+      <c r="H47" s="173"/>
+      <c r="I47" s="173"/>
+      <c r="J47" s="173"/>
+      <c r="K47" s="173"/>
       <c r="L47" s="22"/>
     </row>
     <row r="48" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7911,17 +7911,17 @@
       <c r="B49" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="C49" s="184" t="s">
+      <c r="C49" s="172" t="s">
         <v>74</v>
       </c>
-      <c r="D49" s="175"/>
-      <c r="E49" s="175"/>
-      <c r="F49" s="175"/>
-      <c r="G49" s="175"/>
-      <c r="H49" s="175"/>
-      <c r="I49" s="175"/>
-      <c r="J49" s="175"/>
-      <c r="K49" s="175"/>
+      <c r="D49" s="173"/>
+      <c r="E49" s="173"/>
+      <c r="F49" s="173"/>
+      <c r="G49" s="173"/>
+      <c r="H49" s="173"/>
+      <c r="I49" s="173"/>
+      <c r="J49" s="173"/>
+      <c r="K49" s="173"/>
       <c r="L49" s="13"/>
     </row>
     <row r="50" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7945,18 +7945,18 @@
       <c r="B51" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C51" s="182" t="str">
+      <c r="C51" s="174" t="str">
         <f t="array" ref="C51">IF(C52="","?",C52)&amp;IF(C53="","","; downloaded "&amp;C53)&amp;IF(C54="","","; "&amp;C54)</f>
         <v>https://www.ine.es/jaxiT3/Tabla.htm?t=56934, https://www.ine.es/dyngs/INEbase/es/operacion.htm?c=Estadistica_C&amp;cid=1254736177092; downloaded 2026-05-26</v>
       </c>
-      <c r="D51" s="175"/>
-      <c r="E51" s="175"/>
-      <c r="F51" s="175"/>
-      <c r="G51" s="175"/>
-      <c r="H51" s="175"/>
-      <c r="I51" s="175"/>
-      <c r="J51" s="175"/>
-      <c r="K51" s="175"/>
+      <c r="D51" s="173"/>
+      <c r="E51" s="173"/>
+      <c r="F51" s="173"/>
+      <c r="G51" s="173"/>
+      <c r="H51" s="173"/>
+      <c r="I51" s="173"/>
+      <c r="J51" s="173"/>
+      <c r="K51" s="173"/>
       <c r="L51" s="13"/>
     </row>
     <row r="52" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7964,17 +7964,17 @@
       <c r="B52" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C52" s="183" t="s">
+      <c r="C52" s="175" t="s">
         <v>78</v>
       </c>
-      <c r="D52" s="175"/>
-      <c r="E52" s="175"/>
-      <c r="F52" s="175"/>
-      <c r="G52" s="175"/>
-      <c r="H52" s="175"/>
-      <c r="I52" s="175"/>
-      <c r="J52" s="175"/>
-      <c r="K52" s="175"/>
+      <c r="D52" s="173"/>
+      <c r="E52" s="173"/>
+      <c r="F52" s="173"/>
+      <c r="G52" s="173"/>
+      <c r="H52" s="173"/>
+      <c r="I52" s="173"/>
+      <c r="J52" s="173"/>
+      <c r="K52" s="173"/>
       <c r="L52" s="13"/>
     </row>
     <row r="53" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7982,17 +7982,17 @@
       <c r="B53" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C53" s="183" t="s">
+      <c r="C53" s="175" t="s">
         <v>37</v>
       </c>
-      <c r="D53" s="175"/>
-      <c r="E53" s="175"/>
-      <c r="F53" s="175"/>
-      <c r="G53" s="175"/>
-      <c r="H53" s="175"/>
-      <c r="I53" s="175"/>
-      <c r="J53" s="175"/>
-      <c r="K53" s="175"/>
+      <c r="D53" s="173"/>
+      <c r="E53" s="173"/>
+      <c r="F53" s="173"/>
+      <c r="G53" s="173"/>
+      <c r="H53" s="173"/>
+      <c r="I53" s="173"/>
+      <c r="J53" s="173"/>
+      <c r="K53" s="173"/>
       <c r="L53" s="13"/>
     </row>
     <row r="54" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8000,15 +8000,15 @@
       <c r="B54" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C54" s="184"/>
-      <c r="D54" s="175"/>
-      <c r="E54" s="175"/>
-      <c r="F54" s="175"/>
-      <c r="G54" s="175"/>
-      <c r="H54" s="175"/>
-      <c r="I54" s="175"/>
-      <c r="J54" s="175"/>
-      <c r="K54" s="175"/>
+      <c r="C54" s="172"/>
+      <c r="D54" s="173"/>
+      <c r="E54" s="173"/>
+      <c r="F54" s="173"/>
+      <c r="G54" s="173"/>
+      <c r="H54" s="173"/>
+      <c r="I54" s="173"/>
+      <c r="J54" s="173"/>
+      <c r="K54" s="173"/>
       <c r="L54" s="13"/>
     </row>
     <row r="55" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8016,17 +8016,17 @@
       <c r="B55" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C55" s="184" t="s">
+      <c r="C55" s="172" t="s">
         <v>82</v>
       </c>
-      <c r="D55" s="175"/>
-      <c r="E55" s="175"/>
-      <c r="F55" s="175"/>
-      <c r="G55" s="175"/>
-      <c r="H55" s="175"/>
-      <c r="I55" s="175"/>
-      <c r="J55" s="175"/>
-      <c r="K55" s="175"/>
+      <c r="D55" s="173"/>
+      <c r="E55" s="173"/>
+      <c r="F55" s="173"/>
+      <c r="G55" s="173"/>
+      <c r="H55" s="173"/>
+      <c r="I55" s="173"/>
+      <c r="J55" s="173"/>
+      <c r="K55" s="173"/>
       <c r="L55" s="13"/>
     </row>
     <row r="56" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8034,15 +8034,15 @@
       <c r="B56" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="184"/>
-      <c r="D56" s="175"/>
-      <c r="E56" s="175"/>
-      <c r="F56" s="175"/>
-      <c r="G56" s="175"/>
-      <c r="H56" s="175"/>
-      <c r="I56" s="175"/>
-      <c r="J56" s="175"/>
-      <c r="K56" s="175"/>
+      <c r="C56" s="172"/>
+      <c r="D56" s="173"/>
+      <c r="E56" s="173"/>
+      <c r="F56" s="173"/>
+      <c r="G56" s="173"/>
+      <c r="H56" s="173"/>
+      <c r="I56" s="173"/>
+      <c r="J56" s="173"/>
+      <c r="K56" s="173"/>
       <c r="L56" s="13"/>
     </row>
     <row r="57" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8064,17 +8064,17 @@
       <c r="B58" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="C58" s="177" t="s">
+      <c r="C58" s="176" t="s">
         <v>85</v>
       </c>
-      <c r="D58" s="175"/>
-      <c r="E58" s="175"/>
-      <c r="F58" s="175"/>
-      <c r="G58" s="175"/>
-      <c r="H58" s="175"/>
-      <c r="I58" s="175"/>
-      <c r="J58" s="175"/>
-      <c r="K58" s="175"/>
+      <c r="D58" s="173"/>
+      <c r="E58" s="173"/>
+      <c r="F58" s="173"/>
+      <c r="G58" s="173"/>
+      <c r="H58" s="173"/>
+      <c r="I58" s="173"/>
+      <c r="J58" s="173"/>
+      <c r="K58" s="173"/>
       <c r="L58" s="22"/>
     </row>
     <row r="59" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8153,18 +8153,18 @@
       <c r="B62" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="182" t="str">
+      <c r="C62" s="174" t="str">
         <f t="array" ref="C62">IF(C63="","?",C63)&amp;IF(C64="","","; downloaded "&amp;C64)&amp;IF(C65="","","; "&amp;C65)</f>
         <v>https://ec.europa.eu/eurostat/databrowser/view/demo_mlexpec/default/table; downloaded 2026-05-26</v>
       </c>
-      <c r="D62" s="175"/>
-      <c r="E62" s="175"/>
-      <c r="F62" s="175"/>
-      <c r="G62" s="175"/>
-      <c r="H62" s="175"/>
-      <c r="I62" s="175"/>
-      <c r="J62" s="175"/>
-      <c r="K62" s="175"/>
+      <c r="D62" s="173"/>
+      <c r="E62" s="173"/>
+      <c r="F62" s="173"/>
+      <c r="G62" s="173"/>
+      <c r="H62" s="173"/>
+      <c r="I62" s="173"/>
+      <c r="J62" s="173"/>
+      <c r="K62" s="173"/>
       <c r="L62" s="13"/>
     </row>
     <row r="63" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8172,17 +8172,17 @@
       <c r="B63" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="183" t="s">
+      <c r="C63" s="175" t="s">
         <v>89</v>
       </c>
-      <c r="D63" s="175"/>
-      <c r="E63" s="175"/>
-      <c r="F63" s="175"/>
-      <c r="G63" s="175"/>
-      <c r="H63" s="175"/>
-      <c r="I63" s="175"/>
-      <c r="J63" s="175"/>
-      <c r="K63" s="175"/>
+      <c r="D63" s="173"/>
+      <c r="E63" s="173"/>
+      <c r="F63" s="173"/>
+      <c r="G63" s="173"/>
+      <c r="H63" s="173"/>
+      <c r="I63" s="173"/>
+      <c r="J63" s="173"/>
+      <c r="K63" s="173"/>
       <c r="L63" s="13"/>
     </row>
     <row r="64" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8190,17 +8190,17 @@
       <c r="B64" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C64" s="183" t="s">
+      <c r="C64" s="175" t="s">
         <v>37</v>
       </c>
-      <c r="D64" s="175"/>
-      <c r="E64" s="175"/>
-      <c r="F64" s="175"/>
-      <c r="G64" s="175"/>
-      <c r="H64" s="175"/>
-      <c r="I64" s="175"/>
-      <c r="J64" s="175"/>
-      <c r="K64" s="175"/>
+      <c r="D64" s="173"/>
+      <c r="E64" s="173"/>
+      <c r="F64" s="173"/>
+      <c r="G64" s="173"/>
+      <c r="H64" s="173"/>
+      <c r="I64" s="173"/>
+      <c r="J64" s="173"/>
+      <c r="K64" s="173"/>
       <c r="L64" s="13"/>
     </row>
     <row r="65" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8208,15 +8208,15 @@
       <c r="B65" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C65" s="184"/>
-      <c r="D65" s="175"/>
-      <c r="E65" s="175"/>
-      <c r="F65" s="175"/>
-      <c r="G65" s="175"/>
-      <c r="H65" s="175"/>
-      <c r="I65" s="175"/>
-      <c r="J65" s="175"/>
-      <c r="K65" s="175"/>
+      <c r="C65" s="172"/>
+      <c r="D65" s="173"/>
+      <c r="E65" s="173"/>
+      <c r="F65" s="173"/>
+      <c r="G65" s="173"/>
+      <c r="H65" s="173"/>
+      <c r="I65" s="173"/>
+      <c r="J65" s="173"/>
+      <c r="K65" s="173"/>
       <c r="L65" s="13"/>
     </row>
     <row r="66" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8224,17 +8224,17 @@
       <c r="B66" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C66" s="184" t="s">
+      <c r="C66" s="172" t="s">
         <v>90</v>
       </c>
-      <c r="D66" s="175"/>
-      <c r="E66" s="175"/>
-      <c r="F66" s="175"/>
-      <c r="G66" s="175"/>
-      <c r="H66" s="175"/>
-      <c r="I66" s="175"/>
-      <c r="J66" s="175"/>
-      <c r="K66" s="175"/>
+      <c r="D66" s="173"/>
+      <c r="E66" s="173"/>
+      <c r="F66" s="173"/>
+      <c r="G66" s="173"/>
+      <c r="H66" s="173"/>
+      <c r="I66" s="173"/>
+      <c r="J66" s="173"/>
+      <c r="K66" s="173"/>
       <c r="L66" s="13"/>
     </row>
     <row r="67" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8242,15 +8242,15 @@
       <c r="B67" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C67" s="184"/>
-      <c r="D67" s="175"/>
-      <c r="E67" s="175"/>
-      <c r="F67" s="175"/>
-      <c r="G67" s="175"/>
-      <c r="H67" s="175"/>
-      <c r="I67" s="175"/>
-      <c r="J67" s="175"/>
-      <c r="K67" s="175"/>
+      <c r="C67" s="172"/>
+      <c r="D67" s="173"/>
+      <c r="E67" s="173"/>
+      <c r="F67" s="173"/>
+      <c r="G67" s="173"/>
+      <c r="H67" s="173"/>
+      <c r="I67" s="173"/>
+      <c r="J67" s="173"/>
+      <c r="K67" s="173"/>
       <c r="L67" s="13"/>
     </row>
     <row r="68" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8269,6 +8269,27 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="C31:K31"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C47:K47"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D28:G28"/>
     <mergeCell ref="C67:K67"/>
     <mergeCell ref="C49:K49"/>
     <mergeCell ref="C51:K51"/>
@@ -8283,27 +8304,6 @@
     <mergeCell ref="C63:K63"/>
     <mergeCell ref="C64:K64"/>
     <mergeCell ref="C65:K65"/>
-    <mergeCell ref="C47:K47"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C11:K11"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="C10:K10"/>
-    <mergeCell ref="C31:K31"/>
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C13:K13"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
@@ -8328,20 +8328,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="182" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="178"/>
+      <c r="L1" s="178"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1"/>
@@ -8420,14 +8420,14 @@
       <c r="C4" s="191" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
+      <c r="D4" s="178"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="178"/>
+      <c r="H4" s="178"/>
+      <c r="I4" s="178"/>
+      <c r="J4" s="178"/>
+      <c r="K4" s="178"/>
       <c r="L4" s="49"/>
     </row>
     <row r="5" spans="1:12" ht="26.85" customHeight="1">
@@ -13062,18 +13062,18 @@
       <c r="B111" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C111" s="182" t="str">
+      <c r="C111" s="174" t="str">
         <f t="array" ref="C111">IF(C112="","?",C112)&amp;IF(C113="","","; downloaded "&amp;C113)&amp;IF(C114="","","; "&amp;C114)</f>
         <v>https://www.ine.es/jaxiT3/Tabla.htm?t=56934, https://www.ine.es/jaxiT3/Tabla.htm?t=60128, https://www.ine.es/dyngs/INEbase/es/operacion.htm?c=Estadistica_C&amp;cid=1254736177092; downloaded 2026-05-26</v>
       </c>
-      <c r="D111" s="175"/>
-      <c r="E111" s="175"/>
-      <c r="F111" s="175"/>
-      <c r="G111" s="175"/>
-      <c r="H111" s="175"/>
-      <c r="I111" s="175"/>
-      <c r="J111" s="175"/>
-      <c r="K111" s="175"/>
+      <c r="D111" s="173"/>
+      <c r="E111" s="173"/>
+      <c r="F111" s="173"/>
+      <c r="G111" s="173"/>
+      <c r="H111" s="173"/>
+      <c r="I111" s="173"/>
+      <c r="J111" s="173"/>
+      <c r="K111" s="173"/>
       <c r="L111" s="13"/>
     </row>
     <row r="112" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -13081,17 +13081,17 @@
       <c r="B112" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C112" s="183" t="s">
+      <c r="C112" s="175" t="s">
         <v>301</v>
       </c>
-      <c r="D112" s="175"/>
-      <c r="E112" s="175"/>
-      <c r="F112" s="175"/>
-      <c r="G112" s="175"/>
-      <c r="H112" s="175"/>
-      <c r="I112" s="175"/>
-      <c r="J112" s="175"/>
-      <c r="K112" s="175"/>
+      <c r="D112" s="173"/>
+      <c r="E112" s="173"/>
+      <c r="F112" s="173"/>
+      <c r="G112" s="173"/>
+      <c r="H112" s="173"/>
+      <c r="I112" s="173"/>
+      <c r="J112" s="173"/>
+      <c r="K112" s="173"/>
       <c r="L112" s="13"/>
     </row>
     <row r="113" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -13099,17 +13099,17 @@
       <c r="B113" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C113" s="183" t="s">
+      <c r="C113" s="175" t="s">
         <v>37</v>
       </c>
-      <c r="D113" s="175"/>
-      <c r="E113" s="175"/>
-      <c r="F113" s="175"/>
-      <c r="G113" s="175"/>
-      <c r="H113" s="175"/>
-      <c r="I113" s="175"/>
-      <c r="J113" s="175"/>
-      <c r="K113" s="175"/>
+      <c r="D113" s="173"/>
+      <c r="E113" s="173"/>
+      <c r="F113" s="173"/>
+      <c r="G113" s="173"/>
+      <c r="H113" s="173"/>
+      <c r="I113" s="173"/>
+      <c r="J113" s="173"/>
+      <c r="K113" s="173"/>
       <c r="L113" s="13"/>
     </row>
     <row r="114" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -13117,15 +13117,15 @@
       <c r="B114" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C114" s="184"/>
-      <c r="D114" s="175"/>
-      <c r="E114" s="175"/>
-      <c r="F114" s="175"/>
-      <c r="G114" s="175"/>
-      <c r="H114" s="175"/>
-      <c r="I114" s="175"/>
-      <c r="J114" s="175"/>
-      <c r="K114" s="175"/>
+      <c r="C114" s="172"/>
+      <c r="D114" s="173"/>
+      <c r="E114" s="173"/>
+      <c r="F114" s="173"/>
+      <c r="G114" s="173"/>
+      <c r="H114" s="173"/>
+      <c r="I114" s="173"/>
+      <c r="J114" s="173"/>
+      <c r="K114" s="173"/>
       <c r="L114" s="13"/>
     </row>
     <row r="115" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -13133,17 +13133,17 @@
       <c r="B115" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C115" s="184" t="s">
+      <c r="C115" s="172" t="s">
         <v>302</v>
       </c>
-      <c r="D115" s="175"/>
-      <c r="E115" s="175"/>
-      <c r="F115" s="175"/>
-      <c r="G115" s="175"/>
-      <c r="H115" s="175"/>
-      <c r="I115" s="175"/>
-      <c r="J115" s="175"/>
-      <c r="K115" s="175"/>
+      <c r="D115" s="173"/>
+      <c r="E115" s="173"/>
+      <c r="F115" s="173"/>
+      <c r="G115" s="173"/>
+      <c r="H115" s="173"/>
+      <c r="I115" s="173"/>
+      <c r="J115" s="173"/>
+      <c r="K115" s="173"/>
       <c r="L115" s="13"/>
     </row>
     <row r="116" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -13151,15 +13151,15 @@
       <c r="B116" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C116" s="184"/>
-      <c r="D116" s="175"/>
-      <c r="E116" s="175"/>
-      <c r="F116" s="175"/>
-      <c r="G116" s="175"/>
-      <c r="H116" s="175"/>
-      <c r="I116" s="175"/>
-      <c r="J116" s="175"/>
-      <c r="K116" s="175"/>
+      <c r="C116" s="172"/>
+      <c r="D116" s="173"/>
+      <c r="E116" s="173"/>
+      <c r="F116" s="173"/>
+      <c r="G116" s="173"/>
+      <c r="H116" s="173"/>
+      <c r="I116" s="173"/>
+      <c r="J116" s="173"/>
+      <c r="K116" s="173"/>
       <c r="L116" s="13"/>
     </row>
     <row r="117" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -13184,14 +13184,14 @@
       <c r="C118" s="192" t="s">
         <v>304</v>
       </c>
-      <c r="D118" s="173"/>
-      <c r="E118" s="173"/>
-      <c r="F118" s="173"/>
-      <c r="G118" s="173"/>
-      <c r="H118" s="173"/>
-      <c r="I118" s="173"/>
-      <c r="J118" s="173"/>
-      <c r="K118" s="173"/>
+      <c r="D118" s="178"/>
+      <c r="E118" s="178"/>
+      <c r="F118" s="178"/>
+      <c r="G118" s="178"/>
+      <c r="H118" s="178"/>
+      <c r="I118" s="178"/>
+      <c r="J118" s="178"/>
+      <c r="K118" s="178"/>
       <c r="L118" s="58"/>
     </row>
     <row r="119" spans="1:12" ht="26.85" customHeight="1">
@@ -15642,17 +15642,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C111:K111"/>
+    <mergeCell ref="C112:K112"/>
+    <mergeCell ref="C113:K113"/>
+    <mergeCell ref="C114:K114"/>
     <mergeCell ref="C116:K116"/>
     <mergeCell ref="C5:K5"/>
     <mergeCell ref="C119:K119"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="C118:K118"/>
     <mergeCell ref="C115:K115"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C111:K111"/>
-    <mergeCell ref="C112:K112"/>
-    <mergeCell ref="C113:K113"/>
-    <mergeCell ref="C114:K114"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
@@ -15677,20 +15677,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="182" t="s">
         <v>306</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="178"/>
+      <c r="L1" s="178"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1"/>
@@ -15769,14 +15769,14 @@
       <c r="C4" s="191" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
+      <c r="D4" s="178"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="178"/>
+      <c r="H4" s="178"/>
+      <c r="I4" s="178"/>
+      <c r="J4" s="178"/>
+      <c r="K4" s="178"/>
       <c r="L4" s="49"/>
     </row>
     <row r="5" spans="1:12" ht="26.85" customHeight="1">
@@ -15989,18 +15989,18 @@
       <c r="B13" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="182" t="str">
+      <c r="C13" s="174" t="str">
         <f t="array" ref="C13">IF(C14="","?",C14)&amp;IF(C15="","","; downloaded "&amp;C15)&amp;IF(C16="","","; "&amp;C16)</f>
         <v>Enter URLs here, if you have multiple URLs seperate them with a comma; downloaded yyyy-MM-dd</v>
       </c>
-      <c r="D13" s="175"/>
-      <c r="E13" s="175"/>
-      <c r="F13" s="175"/>
-      <c r="G13" s="175"/>
-      <c r="H13" s="175"/>
-      <c r="I13" s="175"/>
-      <c r="J13" s="175"/>
-      <c r="K13" s="175"/>
+      <c r="D13" s="173"/>
+      <c r="E13" s="173"/>
+      <c r="F13" s="173"/>
+      <c r="G13" s="173"/>
+      <c r="H13" s="173"/>
+      <c r="I13" s="173"/>
+      <c r="J13" s="173"/>
+      <c r="K13" s="173"/>
       <c r="L13" s="13"/>
     </row>
     <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -16008,17 +16008,17 @@
       <c r="B14" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="183" t="s">
+      <c r="C14" s="175" t="s">
         <v>317</v>
       </c>
-      <c r="D14" s="175"/>
-      <c r="E14" s="175"/>
-      <c r="F14" s="175"/>
-      <c r="G14" s="175"/>
-      <c r="H14" s="175"/>
-      <c r="I14" s="175"/>
-      <c r="J14" s="175"/>
-      <c r="K14" s="175"/>
+      <c r="D14" s="173"/>
+      <c r="E14" s="173"/>
+      <c r="F14" s="173"/>
+      <c r="G14" s="173"/>
+      <c r="H14" s="173"/>
+      <c r="I14" s="173"/>
+      <c r="J14" s="173"/>
+      <c r="K14" s="173"/>
       <c r="L14" s="13"/>
     </row>
     <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -16026,17 +16026,17 @@
       <c r="B15" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="183" t="s">
+      <c r="C15" s="175" t="s">
         <v>318</v>
       </c>
-      <c r="D15" s="175"/>
-      <c r="E15" s="175"/>
-      <c r="F15" s="175"/>
-      <c r="G15" s="175"/>
-      <c r="H15" s="175"/>
-      <c r="I15" s="175"/>
-      <c r="J15" s="175"/>
-      <c r="K15" s="175"/>
+      <c r="D15" s="173"/>
+      <c r="E15" s="173"/>
+      <c r="F15" s="173"/>
+      <c r="G15" s="173"/>
+      <c r="H15" s="173"/>
+      <c r="I15" s="173"/>
+      <c r="J15" s="173"/>
+      <c r="K15" s="173"/>
       <c r="L15" s="13"/>
     </row>
     <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -16044,15 +16044,15 @@
       <c r="B16" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="184"/>
-      <c r="D16" s="175"/>
-      <c r="E16" s="175"/>
-      <c r="F16" s="175"/>
-      <c r="G16" s="175"/>
-      <c r="H16" s="175"/>
-      <c r="I16" s="175"/>
-      <c r="J16" s="175"/>
-      <c r="K16" s="175"/>
+      <c r="C16" s="172"/>
+      <c r="D16" s="173"/>
+      <c r="E16" s="173"/>
+      <c r="F16" s="173"/>
+      <c r="G16" s="173"/>
+      <c r="H16" s="173"/>
+      <c r="I16" s="173"/>
+      <c r="J16" s="173"/>
+      <c r="K16" s="173"/>
       <c r="L16" s="13"/>
     </row>
     <row r="17" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -16060,15 +16060,15 @@
       <c r="B17" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="184"/>
-      <c r="D17" s="175"/>
-      <c r="E17" s="175"/>
-      <c r="F17" s="175"/>
-      <c r="G17" s="175"/>
-      <c r="H17" s="175"/>
-      <c r="I17" s="175"/>
-      <c r="J17" s="175"/>
-      <c r="K17" s="175"/>
+      <c r="C17" s="172"/>
+      <c r="D17" s="173"/>
+      <c r="E17" s="173"/>
+      <c r="F17" s="173"/>
+      <c r="G17" s="173"/>
+      <c r="H17" s="173"/>
+      <c r="I17" s="173"/>
+      <c r="J17" s="173"/>
+      <c r="K17" s="173"/>
       <c r="L17" s="13"/>
     </row>
     <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -16076,15 +16076,15 @@
       <c r="B18" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="184"/>
-      <c r="D18" s="175"/>
-      <c r="E18" s="175"/>
-      <c r="F18" s="175"/>
-      <c r="G18" s="175"/>
-      <c r="H18" s="175"/>
-      <c r="I18" s="175"/>
-      <c r="J18" s="175"/>
-      <c r="K18" s="175"/>
+      <c r="C18" s="172"/>
+      <c r="D18" s="173"/>
+      <c r="E18" s="173"/>
+      <c r="F18" s="173"/>
+      <c r="G18" s="173"/>
+      <c r="H18" s="173"/>
+      <c r="I18" s="173"/>
+      <c r="J18" s="173"/>
+      <c r="K18" s="173"/>
       <c r="L18" s="13"/>
     </row>
     <row r="19" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -16109,14 +16109,14 @@
       <c r="C20" s="193" t="s">
         <v>320</v>
       </c>
-      <c r="D20" s="175"/>
-      <c r="E20" s="175"/>
-      <c r="F20" s="175"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="175"/>
-      <c r="I20" s="175"/>
-      <c r="J20" s="175"/>
-      <c r="K20" s="175"/>
+      <c r="D20" s="173"/>
+      <c r="E20" s="173"/>
+      <c r="F20" s="173"/>
+      <c r="G20" s="173"/>
+      <c r="H20" s="173"/>
+      <c r="I20" s="173"/>
+      <c r="J20" s="173"/>
+      <c r="K20" s="173"/>
       <c r="L20" s="22"/>
     </row>
     <row r="21" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -17774,18 +17774,18 @@
       <c r="B59" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="182" t="str">
+      <c r="C59" s="174" t="str">
         <f t="array" ref="C59">IF(C60="","?",C60)&amp;IF(C61="","","; downloaded "&amp;C61)&amp;IF(C62="","","; "&amp;C62)</f>
         <v>https://ec.europa.eu/eurostat/databrowser/view/demo_facbc/default/table?lang=en, https://www.ine.es/jaxiT3/Tabla.htm?t=60128, https://www.ine.es/jaxiT3/Tabla.htm?t=56934; downloaded 2026-05-26</v>
       </c>
-      <c r="D59" s="175"/>
-      <c r="E59" s="175"/>
-      <c r="F59" s="175"/>
-      <c r="G59" s="175"/>
-      <c r="H59" s="175"/>
-      <c r="I59" s="175"/>
-      <c r="J59" s="175"/>
-      <c r="K59" s="175"/>
+      <c r="D59" s="173"/>
+      <c r="E59" s="173"/>
+      <c r="F59" s="173"/>
+      <c r="G59" s="173"/>
+      <c r="H59" s="173"/>
+      <c r="I59" s="173"/>
+      <c r="J59" s="173"/>
+      <c r="K59" s="173"/>
       <c r="L59" s="13"/>
     </row>
     <row r="60" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -17793,17 +17793,17 @@
       <c r="B60" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C60" s="183" t="s">
+      <c r="C60" s="175" t="s">
         <v>393</v>
       </c>
-      <c r="D60" s="175"/>
-      <c r="E60" s="175"/>
-      <c r="F60" s="175"/>
-      <c r="G60" s="175"/>
-      <c r="H60" s="175"/>
-      <c r="I60" s="175"/>
-      <c r="J60" s="175"/>
-      <c r="K60" s="175"/>
+      <c r="D60" s="173"/>
+      <c r="E60" s="173"/>
+      <c r="F60" s="173"/>
+      <c r="G60" s="173"/>
+      <c r="H60" s="173"/>
+      <c r="I60" s="173"/>
+      <c r="J60" s="173"/>
+      <c r="K60" s="173"/>
       <c r="L60" s="13"/>
     </row>
     <row r="61" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -17811,17 +17811,17 @@
       <c r="B61" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C61" s="183" t="s">
+      <c r="C61" s="175" t="s">
         <v>37</v>
       </c>
-      <c r="D61" s="175"/>
-      <c r="E61" s="175"/>
-      <c r="F61" s="175"/>
-      <c r="G61" s="175"/>
-      <c r="H61" s="175"/>
-      <c r="I61" s="175"/>
-      <c r="J61" s="175"/>
-      <c r="K61" s="175"/>
+      <c r="D61" s="173"/>
+      <c r="E61" s="173"/>
+      <c r="F61" s="173"/>
+      <c r="G61" s="173"/>
+      <c r="H61" s="173"/>
+      <c r="I61" s="173"/>
+      <c r="J61" s="173"/>
+      <c r="K61" s="173"/>
       <c r="L61" s="13"/>
     </row>
     <row r="62" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -17829,15 +17829,15 @@
       <c r="B62" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C62" s="184"/>
-      <c r="D62" s="175"/>
-      <c r="E62" s="175"/>
-      <c r="F62" s="175"/>
-      <c r="G62" s="175"/>
-      <c r="H62" s="175"/>
-      <c r="I62" s="175"/>
-      <c r="J62" s="175"/>
-      <c r="K62" s="175"/>
+      <c r="C62" s="172"/>
+      <c r="D62" s="173"/>
+      <c r="E62" s="173"/>
+      <c r="F62" s="173"/>
+      <c r="G62" s="173"/>
+      <c r="H62" s="173"/>
+      <c r="I62" s="173"/>
+      <c r="J62" s="173"/>
+      <c r="K62" s="173"/>
       <c r="L62" s="13"/>
     </row>
     <row r="63" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -17845,17 +17845,17 @@
       <c r="B63" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C63" s="184" t="s">
+      <c r="C63" s="172" t="s">
         <v>394</v>
       </c>
-      <c r="D63" s="175"/>
-      <c r="E63" s="175"/>
-      <c r="F63" s="175"/>
-      <c r="G63" s="175"/>
-      <c r="H63" s="175"/>
-      <c r="I63" s="175"/>
-      <c r="J63" s="175"/>
-      <c r="K63" s="175"/>
+      <c r="D63" s="173"/>
+      <c r="E63" s="173"/>
+      <c r="F63" s="173"/>
+      <c r="G63" s="173"/>
+      <c r="H63" s="173"/>
+      <c r="I63" s="173"/>
+      <c r="J63" s="173"/>
+      <c r="K63" s="173"/>
       <c r="L63" s="13"/>
     </row>
     <row r="64" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -17863,15 +17863,15 @@
       <c r="B64" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C64" s="184"/>
-      <c r="D64" s="175"/>
-      <c r="E64" s="175"/>
-      <c r="F64" s="175"/>
-      <c r="G64" s="175"/>
-      <c r="H64" s="175"/>
-      <c r="I64" s="175"/>
-      <c r="J64" s="175"/>
-      <c r="K64" s="175"/>
+      <c r="C64" s="172"/>
+      <c r="D64" s="173"/>
+      <c r="E64" s="173"/>
+      <c r="F64" s="173"/>
+      <c r="G64" s="173"/>
+      <c r="H64" s="173"/>
+      <c r="I64" s="173"/>
+      <c r="J64" s="173"/>
+      <c r="K64" s="173"/>
       <c r="L64" s="13"/>
     </row>
     <row r="65" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -17896,14 +17896,14 @@
       <c r="C66" s="192" t="s">
         <v>304</v>
       </c>
-      <c r="D66" s="173"/>
-      <c r="E66" s="173"/>
-      <c r="F66" s="173"/>
-      <c r="G66" s="173"/>
-      <c r="H66" s="173"/>
-      <c r="I66" s="173"/>
-      <c r="J66" s="173"/>
-      <c r="K66" s="173"/>
+      <c r="D66" s="178"/>
+      <c r="E66" s="178"/>
+      <c r="F66" s="178"/>
+      <c r="G66" s="178"/>
+      <c r="H66" s="178"/>
+      <c r="I66" s="178"/>
+      <c r="J66" s="178"/>
+      <c r="K66" s="178"/>
       <c r="L66" s="58"/>
     </row>
     <row r="67" spans="1:12" ht="26.85" customHeight="1">
@@ -18828,6 +18828,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C59:K59"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="C61:K61"/>
+    <mergeCell ref="C62:K62"/>
+    <mergeCell ref="C4:K4"/>
     <mergeCell ref="C64:K64"/>
     <mergeCell ref="C20:K20"/>
     <mergeCell ref="C67:K67"/>
@@ -18840,12 +18846,6 @@
     <mergeCell ref="C66:K66"/>
     <mergeCell ref="C63:K63"/>
     <mergeCell ref="C17:K17"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C59:K59"/>
-    <mergeCell ref="C60:K60"/>
-    <mergeCell ref="C61:K61"/>
-    <mergeCell ref="C62:K62"/>
-    <mergeCell ref="C4:K4"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
@@ -18870,20 +18870,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="182" t="s">
         <v>401</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="178"/>
+      <c r="L1" s="178"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1"/>
@@ -18980,14 +18980,14 @@
       <c r="C5" s="193" t="s">
         <v>403</v>
       </c>
-      <c r="D5" s="175"/>
-      <c r="E5" s="175"/>
-      <c r="F5" s="175"/>
-      <c r="G5" s="175"/>
-      <c r="H5" s="175"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="175"/>
-      <c r="K5" s="175"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="173"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="173"/>
+      <c r="H5" s="173"/>
+      <c r="I5" s="173"/>
+      <c r="J5" s="173"/>
+      <c r="K5" s="173"/>
       <c r="L5" s="22"/>
     </row>
     <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -23570,18 +23570,18 @@
       <c r="B109" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C109" s="182" t="str">
+      <c r="C109" s="174" t="str">
         <f t="array" ref="C109">IF(C110="","?",C110)&amp;IF(C111="","","; downloaded "&amp;C111)&amp;IF(C112="","","; "&amp;C112)</f>
         <v>https://ec.europa.eu/eurostat/databrowser/view/demo_magec/default/table?lang=en; downloaded 2026-05-26</v>
       </c>
-      <c r="D109" s="175"/>
-      <c r="E109" s="175"/>
-      <c r="F109" s="175"/>
-      <c r="G109" s="175"/>
-      <c r="H109" s="175"/>
-      <c r="I109" s="175"/>
-      <c r="J109" s="175"/>
-      <c r="K109" s="175"/>
+      <c r="D109" s="173"/>
+      <c r="E109" s="173"/>
+      <c r="F109" s="173"/>
+      <c r="G109" s="173"/>
+      <c r="H109" s="173"/>
+      <c r="I109" s="173"/>
+      <c r="J109" s="173"/>
+      <c r="K109" s="173"/>
       <c r="L109" s="13"/>
     </row>
     <row r="110" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -23589,17 +23589,17 @@
       <c r="B110" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C110" s="183" t="s">
+      <c r="C110" s="175" t="s">
         <v>606</v>
       </c>
-      <c r="D110" s="175"/>
-      <c r="E110" s="175"/>
-      <c r="F110" s="175"/>
-      <c r="G110" s="175"/>
-      <c r="H110" s="175"/>
-      <c r="I110" s="175"/>
-      <c r="J110" s="175"/>
-      <c r="K110" s="175"/>
+      <c r="D110" s="173"/>
+      <c r="E110" s="173"/>
+      <c r="F110" s="173"/>
+      <c r="G110" s="173"/>
+      <c r="H110" s="173"/>
+      <c r="I110" s="173"/>
+      <c r="J110" s="173"/>
+      <c r="K110" s="173"/>
       <c r="L110" s="13"/>
     </row>
     <row r="111" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -23607,17 +23607,17 @@
       <c r="B111" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C111" s="183" t="s">
+      <c r="C111" s="175" t="s">
         <v>37</v>
       </c>
-      <c r="D111" s="175"/>
-      <c r="E111" s="175"/>
-      <c r="F111" s="175"/>
-      <c r="G111" s="175"/>
-      <c r="H111" s="175"/>
-      <c r="I111" s="175"/>
-      <c r="J111" s="175"/>
-      <c r="K111" s="175"/>
+      <c r="D111" s="173"/>
+      <c r="E111" s="173"/>
+      <c r="F111" s="173"/>
+      <c r="G111" s="173"/>
+      <c r="H111" s="173"/>
+      <c r="I111" s="173"/>
+      <c r="J111" s="173"/>
+      <c r="K111" s="173"/>
       <c r="L111" s="13"/>
     </row>
     <row r="112" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -23625,15 +23625,15 @@
       <c r="B112" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C112" s="184"/>
-      <c r="D112" s="175"/>
-      <c r="E112" s="175"/>
-      <c r="F112" s="175"/>
-      <c r="G112" s="175"/>
-      <c r="H112" s="175"/>
-      <c r="I112" s="175"/>
-      <c r="J112" s="175"/>
-      <c r="K112" s="175"/>
+      <c r="C112" s="172"/>
+      <c r="D112" s="173"/>
+      <c r="E112" s="173"/>
+      <c r="F112" s="173"/>
+      <c r="G112" s="173"/>
+      <c r="H112" s="173"/>
+      <c r="I112" s="173"/>
+      <c r="J112" s="173"/>
+      <c r="K112" s="173"/>
       <c r="L112" s="13"/>
     </row>
     <row r="113" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -23641,17 +23641,17 @@
       <c r="B113" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C113" s="184" t="s">
+      <c r="C113" s="172" t="s">
         <v>607</v>
       </c>
-      <c r="D113" s="175"/>
-      <c r="E113" s="175"/>
-      <c r="F113" s="175"/>
-      <c r="G113" s="175"/>
-      <c r="H113" s="175"/>
-      <c r="I113" s="175"/>
-      <c r="J113" s="175"/>
-      <c r="K113" s="175"/>
+      <c r="D113" s="173"/>
+      <c r="E113" s="173"/>
+      <c r="F113" s="173"/>
+      <c r="G113" s="173"/>
+      <c r="H113" s="173"/>
+      <c r="I113" s="173"/>
+      <c r="J113" s="173"/>
+      <c r="K113" s="173"/>
       <c r="L113" s="13"/>
     </row>
     <row r="114" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -23659,15 +23659,15 @@
       <c r="B114" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C114" s="184"/>
-      <c r="D114" s="175"/>
-      <c r="E114" s="175"/>
-      <c r="F114" s="175"/>
-      <c r="G114" s="175"/>
-      <c r="H114" s="175"/>
-      <c r="I114" s="175"/>
-      <c r="J114" s="175"/>
-      <c r="K114" s="175"/>
+      <c r="C114" s="172"/>
+      <c r="D114" s="173"/>
+      <c r="E114" s="173"/>
+      <c r="F114" s="173"/>
+      <c r="G114" s="173"/>
+      <c r="H114" s="173"/>
+      <c r="I114" s="173"/>
+      <c r="J114" s="173"/>
+      <c r="K114" s="173"/>
       <c r="L114" s="13"/>
     </row>
     <row r="115" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -23692,14 +23692,14 @@
       <c r="C116" s="196" t="s">
         <v>304</v>
       </c>
-      <c r="D116" s="175"/>
-      <c r="E116" s="175"/>
-      <c r="F116" s="175"/>
-      <c r="G116" s="175"/>
-      <c r="H116" s="175"/>
-      <c r="I116" s="175"/>
-      <c r="J116" s="175"/>
-      <c r="K116" s="175"/>
+      <c r="D116" s="173"/>
+      <c r="E116" s="173"/>
+      <c r="F116" s="173"/>
+      <c r="G116" s="173"/>
+      <c r="H116" s="173"/>
+      <c r="I116" s="173"/>
+      <c r="J116" s="173"/>
+      <c r="K116" s="173"/>
       <c r="L116" s="58"/>
     </row>
     <row r="117" spans="1:12" ht="26.85" customHeight="1">
@@ -23710,13 +23710,13 @@
       <c r="C117" s="194" t="s">
         <v>608</v>
       </c>
-      <c r="D117" s="175"/>
-      <c r="E117" s="175"/>
-      <c r="F117" s="175"/>
-      <c r="G117" s="175"/>
-      <c r="H117" s="175"/>
-      <c r="I117" s="175"/>
-      <c r="J117" s="175"/>
+      <c r="D117" s="173"/>
+      <c r="E117" s="173"/>
+      <c r="F117" s="173"/>
+      <c r="G117" s="173"/>
+      <c r="H117" s="173"/>
+      <c r="I117" s="173"/>
+      <c r="J117" s="173"/>
       <c r="K117" s="195"/>
       <c r="L117" s="104"/>
     </row>
@@ -26150,17 +26150,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C109:K109"/>
+    <mergeCell ref="C110:K110"/>
+    <mergeCell ref="C111:K111"/>
+    <mergeCell ref="C112:K112"/>
     <mergeCell ref="C114:K114"/>
     <mergeCell ref="C5:K5"/>
     <mergeCell ref="C117:K117"/>
     <mergeCell ref="C116:K116"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="C113:K113"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C109:K109"/>
-    <mergeCell ref="C110:K110"/>
-    <mergeCell ref="C111:K111"/>
-    <mergeCell ref="C112:K112"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
@@ -26185,20 +26185,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="182" t="s">
         <v>609</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="178"/>
+      <c r="L1" s="178"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1"/>
@@ -26277,14 +26277,14 @@
       <c r="C4" s="191" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
+      <c r="D4" s="178"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="178"/>
+      <c r="H4" s="178"/>
+      <c r="I4" s="178"/>
+      <c r="J4" s="178"/>
+      <c r="K4" s="178"/>
       <c r="L4" s="49"/>
     </row>
     <row r="5" spans="1:12" ht="26.85" customHeight="1">
@@ -31076,18 +31076,18 @@
       <c r="B113" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C113" s="182" t="str">
+      <c r="C113" s="174" t="str">
         <f t="array" ref="C113">IF(C114="","?",C114)&amp;IF(C115="","","; downloaded "&amp;C115)&amp;IF(C116="","","; "&amp;C116)</f>
         <v>https://ec.europa.eu/eurostat/databrowser/view/migr_imm3ctb/default/table, https://ec.europa.eu/eurostat/databrowser/view/migr_emi4ctb/default/table; downloaded 2026-05-26; we used the 10-year average number of the migration balance (2015-2024); the numbers are binomially distributed between the age of 5 and 54</v>
       </c>
-      <c r="D113" s="175"/>
-      <c r="E113" s="175"/>
-      <c r="F113" s="175"/>
-      <c r="G113" s="175"/>
-      <c r="H113" s="175"/>
-      <c r="I113" s="175"/>
-      <c r="J113" s="175"/>
-      <c r="K113" s="175"/>
+      <c r="D113" s="173"/>
+      <c r="E113" s="173"/>
+      <c r="F113" s="173"/>
+      <c r="G113" s="173"/>
+      <c r="H113" s="173"/>
+      <c r="I113" s="173"/>
+      <c r="J113" s="173"/>
+      <c r="K113" s="173"/>
       <c r="L113" s="13"/>
     </row>
     <row r="114" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -31095,17 +31095,17 @@
       <c r="B114" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C114" s="183" t="s">
+      <c r="C114" s="175" t="s">
         <v>716</v>
       </c>
-      <c r="D114" s="175"/>
-      <c r="E114" s="175"/>
-      <c r="F114" s="175"/>
-      <c r="G114" s="175"/>
-      <c r="H114" s="175"/>
-      <c r="I114" s="175"/>
-      <c r="J114" s="175"/>
-      <c r="K114" s="175"/>
+      <c r="D114" s="173"/>
+      <c r="E114" s="173"/>
+      <c r="F114" s="173"/>
+      <c r="G114" s="173"/>
+      <c r="H114" s="173"/>
+      <c r="I114" s="173"/>
+      <c r="J114" s="173"/>
+      <c r="K114" s="173"/>
       <c r="L114" s="13"/>
     </row>
     <row r="115" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -31131,17 +31131,17 @@
       <c r="B116" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C116" s="200" t="s">
+      <c r="C116" s="202" t="s">
         <v>717</v>
       </c>
-      <c r="D116" s="173"/>
-      <c r="E116" s="173"/>
-      <c r="F116" s="173"/>
-      <c r="G116" s="173"/>
-      <c r="H116" s="173"/>
-      <c r="I116" s="173"/>
-      <c r="J116" s="173"/>
-      <c r="K116" s="173"/>
+      <c r="D116" s="178"/>
+      <c r="E116" s="178"/>
+      <c r="F116" s="178"/>
+      <c r="G116" s="178"/>
+      <c r="H116" s="178"/>
+      <c r="I116" s="178"/>
+      <c r="J116" s="178"/>
+      <c r="K116" s="178"/>
       <c r="L116" s="13"/>
     </row>
     <row r="117" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -31149,7 +31149,7 @@
       <c r="B117" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C117" s="201" t="s">
+      <c r="C117" s="200" t="s">
         <v>718</v>
       </c>
       <c r="D117" s="186"/>
@@ -31167,15 +31167,15 @@
       <c r="B118" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C118" s="184"/>
-      <c r="D118" s="175"/>
-      <c r="E118" s="175"/>
-      <c r="F118" s="175"/>
-      <c r="G118" s="175"/>
-      <c r="H118" s="175"/>
-      <c r="I118" s="175"/>
-      <c r="J118" s="175"/>
-      <c r="K118" s="175"/>
+      <c r="C118" s="172"/>
+      <c r="D118" s="173"/>
+      <c r="E118" s="173"/>
+      <c r="F118" s="173"/>
+      <c r="G118" s="173"/>
+      <c r="H118" s="173"/>
+      <c r="I118" s="173"/>
+      <c r="J118" s="173"/>
+      <c r="K118" s="173"/>
       <c r="L118" s="13"/>
     </row>
     <row r="119" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -31200,14 +31200,14 @@
       <c r="C120" s="196" t="s">
         <v>304</v>
       </c>
-      <c r="D120" s="175"/>
-      <c r="E120" s="175"/>
-      <c r="F120" s="175"/>
-      <c r="G120" s="175"/>
-      <c r="H120" s="175"/>
-      <c r="I120" s="175"/>
-      <c r="J120" s="175"/>
-      <c r="K120" s="175"/>
+      <c r="D120" s="173"/>
+      <c r="E120" s="173"/>
+      <c r="F120" s="173"/>
+      <c r="G120" s="173"/>
+      <c r="H120" s="173"/>
+      <c r="I120" s="173"/>
+      <c r="J120" s="173"/>
+      <c r="K120" s="173"/>
       <c r="L120" s="58"/>
     </row>
     <row r="121" spans="1:12" ht="32.1" customHeight="1">
@@ -31218,14 +31218,14 @@
       <c r="C121" s="193" t="s">
         <v>720</v>
       </c>
-      <c r="D121" s="175"/>
-      <c r="E121" s="175"/>
-      <c r="F121" s="175"/>
-      <c r="G121" s="175"/>
-      <c r="H121" s="175"/>
-      <c r="I121" s="175"/>
-      <c r="J121" s="175"/>
-      <c r="K121" s="175"/>
+      <c r="D121" s="173"/>
+      <c r="E121" s="173"/>
+      <c r="F121" s="173"/>
+      <c r="G121" s="173"/>
+      <c r="H121" s="173"/>
+      <c r="I121" s="173"/>
+      <c r="J121" s="173"/>
+      <c r="K121" s="173"/>
       <c r="L121" s="22"/>
     </row>
     <row r="122" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -33934,18 +33934,18 @@
       <c r="B201" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C201" s="182" t="str">
+      <c r="C201" s="174" t="str">
         <f t="array" ref="C201">IF(C202="","?",C202)&amp;IF(C203="","","; downloaded "&amp;C203)&amp;IF(C204="","","; "&amp;C204)</f>
         <v>https://ec.europa.eu/eurostat/databrowser/view/migr_imm3ctb/default/table, https://www.ine.es/jaxiT3/Tabla.htm?t=69687; downloaded 2026-05-26</v>
       </c>
-      <c r="D201" s="175"/>
-      <c r="E201" s="175"/>
-      <c r="F201" s="175"/>
-      <c r="G201" s="175"/>
-      <c r="H201" s="175"/>
-      <c r="I201" s="175"/>
-      <c r="J201" s="175"/>
-      <c r="K201" s="175"/>
+      <c r="D201" s="173"/>
+      <c r="E201" s="173"/>
+      <c r="F201" s="173"/>
+      <c r="G201" s="173"/>
+      <c r="H201" s="173"/>
+      <c r="I201" s="173"/>
+      <c r="J201" s="173"/>
+      <c r="K201" s="173"/>
       <c r="L201" s="13"/>
     </row>
     <row r="202" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -33953,17 +33953,17 @@
       <c r="B202" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C202" s="183" t="s">
+      <c r="C202" s="175" t="s">
         <v>722</v>
       </c>
-      <c r="D202" s="175"/>
-      <c r="E202" s="175"/>
-      <c r="F202" s="175"/>
-      <c r="G202" s="175"/>
-      <c r="H202" s="175"/>
-      <c r="I202" s="175"/>
-      <c r="J202" s="175"/>
-      <c r="K202" s="175"/>
+      <c r="D202" s="173"/>
+      <c r="E202" s="173"/>
+      <c r="F202" s="173"/>
+      <c r="G202" s="173"/>
+      <c r="H202" s="173"/>
+      <c r="I202" s="173"/>
+      <c r="J202" s="173"/>
+      <c r="K202" s="173"/>
       <c r="L202" s="13"/>
     </row>
     <row r="203" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -33971,17 +33971,17 @@
       <c r="B203" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C203" s="183" t="s">
+      <c r="C203" s="175" t="s">
         <v>37</v>
       </c>
-      <c r="D203" s="175"/>
-      <c r="E203" s="175"/>
-      <c r="F203" s="175"/>
-      <c r="G203" s="175"/>
-      <c r="H203" s="175"/>
-      <c r="I203" s="175"/>
-      <c r="J203" s="175"/>
-      <c r="K203" s="175"/>
+      <c r="D203" s="173"/>
+      <c r="E203" s="173"/>
+      <c r="F203" s="173"/>
+      <c r="G203" s="173"/>
+      <c r="H203" s="173"/>
+      <c r="I203" s="173"/>
+      <c r="J203" s="173"/>
+      <c r="K203" s="173"/>
       <c r="L203" s="13"/>
     </row>
     <row r="204" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -34005,17 +34005,17 @@
       <c r="B205" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C205" s="202" t="s">
+      <c r="C205" s="201" t="s">
         <v>723</v>
       </c>
-      <c r="D205" s="173"/>
-      <c r="E205" s="173"/>
-      <c r="F205" s="173"/>
-      <c r="G205" s="173"/>
-      <c r="H205" s="173"/>
-      <c r="I205" s="173"/>
-      <c r="J205" s="173"/>
-      <c r="K205" s="173"/>
+      <c r="D205" s="178"/>
+      <c r="E205" s="178"/>
+      <c r="F205" s="178"/>
+      <c r="G205" s="178"/>
+      <c r="H205" s="178"/>
+      <c r="I205" s="178"/>
+      <c r="J205" s="178"/>
+      <c r="K205" s="178"/>
       <c r="L205" s="13"/>
     </row>
     <row r="206" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -34023,7 +34023,7 @@
       <c r="B206" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C206" s="201"/>
+      <c r="C206" s="200"/>
       <c r="D206" s="186"/>
       <c r="E206" s="186"/>
       <c r="F206" s="186"/>
@@ -34056,14 +34056,14 @@
       <c r="C208" s="193" t="s">
         <v>725</v>
       </c>
-      <c r="D208" s="175"/>
-      <c r="E208" s="175"/>
-      <c r="F208" s="175"/>
-      <c r="G208" s="175"/>
-      <c r="H208" s="175"/>
-      <c r="I208" s="175"/>
-      <c r="J208" s="175"/>
-      <c r="K208" s="175"/>
+      <c r="D208" s="173"/>
+      <c r="E208" s="173"/>
+      <c r="F208" s="173"/>
+      <c r="G208" s="173"/>
+      <c r="H208" s="173"/>
+      <c r="I208" s="173"/>
+      <c r="J208" s="173"/>
+      <c r="K208" s="173"/>
       <c r="L208" s="22"/>
     </row>
     <row r="209" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -36772,18 +36772,18 @@
       <c r="B288" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C288" s="182" t="str">
+      <c r="C288" s="174" t="str">
         <f t="array" ref="C288">IF(C289="","?",C289)&amp;IF(C290="","","; downloaded "&amp;C290)&amp;IF(C291="","","; "&amp;C291)</f>
         <v>https://ec.europa.eu/eurostat/databrowser/view/migr_emi4ctb/default/table, https://www.ine.es/jaxiT3/Tabla.htm?t=69702; downloaded 2026-05-26</v>
       </c>
-      <c r="D288" s="175"/>
-      <c r="E288" s="175"/>
-      <c r="F288" s="175"/>
-      <c r="G288" s="175"/>
-      <c r="H288" s="175"/>
-      <c r="I288" s="175"/>
-      <c r="J288" s="175"/>
-      <c r="K288" s="175"/>
+      <c r="D288" s="173"/>
+      <c r="E288" s="173"/>
+      <c r="F288" s="173"/>
+      <c r="G288" s="173"/>
+      <c r="H288" s="173"/>
+      <c r="I288" s="173"/>
+      <c r="J288" s="173"/>
+      <c r="K288" s="173"/>
       <c r="L288" s="13"/>
     </row>
     <row r="289" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -36791,17 +36791,17 @@
       <c r="B289" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C289" s="183" t="s">
+      <c r="C289" s="175" t="s">
         <v>727</v>
       </c>
-      <c r="D289" s="175"/>
-      <c r="E289" s="175"/>
-      <c r="F289" s="175"/>
-      <c r="G289" s="175"/>
-      <c r="H289" s="175"/>
-      <c r="I289" s="175"/>
-      <c r="J289" s="175"/>
-      <c r="K289" s="175"/>
+      <c r="D289" s="173"/>
+      <c r="E289" s="173"/>
+      <c r="F289" s="173"/>
+      <c r="G289" s="173"/>
+      <c r="H289" s="173"/>
+      <c r="I289" s="173"/>
+      <c r="J289" s="173"/>
+      <c r="K289" s="173"/>
       <c r="L289" s="13"/>
     </row>
     <row r="290" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -36809,17 +36809,17 @@
       <c r="B290" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C290" s="183" t="s">
+      <c r="C290" s="175" t="s">
         <v>37</v>
       </c>
-      <c r="D290" s="175"/>
-      <c r="E290" s="175"/>
-      <c r="F290" s="175"/>
-      <c r="G290" s="175"/>
-      <c r="H290" s="175"/>
-      <c r="I290" s="175"/>
-      <c r="J290" s="175"/>
-      <c r="K290" s="175"/>
+      <c r="D290" s="173"/>
+      <c r="E290" s="173"/>
+      <c r="F290" s="173"/>
+      <c r="G290" s="173"/>
+      <c r="H290" s="173"/>
+      <c r="I290" s="173"/>
+      <c r="J290" s="173"/>
+      <c r="K290" s="173"/>
       <c r="L290" s="13"/>
     </row>
     <row r="291" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -36843,7 +36843,7 @@
       <c r="B292" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C292" s="201" t="s">
+      <c r="C292" s="200" t="s">
         <v>728</v>
       </c>
       <c r="D292" s="186"/>
@@ -36861,15 +36861,15 @@
       <c r="B293" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C293" s="184"/>
-      <c r="D293" s="175"/>
-      <c r="E293" s="175"/>
-      <c r="F293" s="175"/>
-      <c r="G293" s="175"/>
-      <c r="H293" s="175"/>
-      <c r="I293" s="175"/>
-      <c r="J293" s="175"/>
-      <c r="K293" s="175"/>
+      <c r="C293" s="172"/>
+      <c r="D293" s="173"/>
+      <c r="E293" s="173"/>
+      <c r="F293" s="173"/>
+      <c r="G293" s="173"/>
+      <c r="H293" s="173"/>
+      <c r="I293" s="173"/>
+      <c r="J293" s="173"/>
+      <c r="K293" s="173"/>
       <c r="L293" s="13"/>
     </row>
     <row r="294" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -36888,12 +36888,11 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C288:K288"/>
-    <mergeCell ref="C289:K289"/>
-    <mergeCell ref="C290:K290"/>
-    <mergeCell ref="C291:K291"/>
-    <mergeCell ref="C293:K293"/>
-    <mergeCell ref="C292:K292"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C113:K113"/>
+    <mergeCell ref="C114:K114"/>
+    <mergeCell ref="C115:K115"/>
+    <mergeCell ref="C116:K116"/>
     <mergeCell ref="C118:K118"/>
     <mergeCell ref="C5:K5"/>
     <mergeCell ref="C121:K121"/>
@@ -36907,11 +36906,12 @@
     <mergeCell ref="C206:K206"/>
     <mergeCell ref="C117:K117"/>
     <mergeCell ref="C205:K205"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C113:K113"/>
-    <mergeCell ref="C114:K114"/>
-    <mergeCell ref="C115:K115"/>
-    <mergeCell ref="C116:K116"/>
+    <mergeCell ref="C288:K288"/>
+    <mergeCell ref="C289:K289"/>
+    <mergeCell ref="C290:K290"/>
+    <mergeCell ref="C291:K291"/>
+    <mergeCell ref="C293:K293"/>
+    <mergeCell ref="C292:K292"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
@@ -36936,20 +36936,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="182" t="s">
         <v>729</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="178"/>
+      <c r="L1" s="178"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1"/>
@@ -37028,14 +37028,14 @@
       <c r="C4" s="192" t="s">
         <v>304</v>
       </c>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
+      <c r="D4" s="178"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="178"/>
+      <c r="H4" s="178"/>
+      <c r="I4" s="178"/>
+      <c r="J4" s="178"/>
+      <c r="K4" s="178"/>
       <c r="L4" s="49"/>
     </row>
     <row r="5" spans="1:12" ht="26.85" customHeight="1">
@@ -43676,20 +43676,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="182" t="s">
         <v>1501</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="178"/>
+      <c r="L1" s="178"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1"/>
@@ -43768,14 +43768,14 @@
       <c r="C4" s="192" t="s">
         <v>304</v>
       </c>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
+      <c r="D4" s="178"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="178"/>
+      <c r="H4" s="178"/>
+      <c r="I4" s="178"/>
+      <c r="J4" s="178"/>
+      <c r="K4" s="178"/>
       <c r="L4" s="49"/>
     </row>
     <row r="5" spans="1:12" ht="26.85" customHeight="1">
@@ -45693,18 +45693,18 @@
       <c r="B87" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C87" s="182" t="str">
+      <c r="C87" s="174" t="str">
         <f t="array" ref="C87">IF(C88="","?",C88)&amp;IF(C89="","","; downloaded "&amp;C89)&amp;IF(C90="","","; "&amp;C90)</f>
         <v>https://ec.europa.eu/eurostat/databrowser/view/migr_acq/default/table; downloaded 2026-05-26</v>
       </c>
-      <c r="D87" s="175"/>
-      <c r="E87" s="175"/>
-      <c r="F87" s="175"/>
-      <c r="G87" s="175"/>
-      <c r="H87" s="175"/>
-      <c r="I87" s="175"/>
-      <c r="J87" s="175"/>
-      <c r="K87" s="175"/>
+      <c r="D87" s="173"/>
+      <c r="E87" s="173"/>
+      <c r="F87" s="173"/>
+      <c r="G87" s="173"/>
+      <c r="H87" s="173"/>
+      <c r="I87" s="173"/>
+      <c r="J87" s="173"/>
+      <c r="K87" s="173"/>
       <c r="L87" s="13"/>
     </row>
     <row r="88" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -45712,17 +45712,17 @@
       <c r="B88" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C88" s="183" t="s">
+      <c r="C88" s="175" t="s">
         <v>1504</v>
       </c>
-      <c r="D88" s="175"/>
-      <c r="E88" s="175"/>
-      <c r="F88" s="175"/>
-      <c r="G88" s="175"/>
-      <c r="H88" s="175"/>
-      <c r="I88" s="175"/>
-      <c r="J88" s="175"/>
-      <c r="K88" s="175"/>
+      <c r="D88" s="173"/>
+      <c r="E88" s="173"/>
+      <c r="F88" s="173"/>
+      <c r="G88" s="173"/>
+      <c r="H88" s="173"/>
+      <c r="I88" s="173"/>
+      <c r="J88" s="173"/>
+      <c r="K88" s="173"/>
       <c r="L88" s="13"/>
     </row>
     <row r="89" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -45730,17 +45730,17 @@
       <c r="B89" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C89" s="183" t="s">
+      <c r="C89" s="175" t="s">
         <v>37</v>
       </c>
-      <c r="D89" s="175"/>
-      <c r="E89" s="175"/>
-      <c r="F89" s="175"/>
-      <c r="G89" s="175"/>
-      <c r="H89" s="175"/>
-      <c r="I89" s="175"/>
-      <c r="J89" s="175"/>
-      <c r="K89" s="175"/>
+      <c r="D89" s="173"/>
+      <c r="E89" s="173"/>
+      <c r="F89" s="173"/>
+      <c r="G89" s="173"/>
+      <c r="H89" s="173"/>
+      <c r="I89" s="173"/>
+      <c r="J89" s="173"/>
+      <c r="K89" s="173"/>
       <c r="L89" s="13"/>
     </row>
     <row r="90" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -45764,7 +45764,7 @@
       <c r="B91" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C91" s="201" t="s">
+      <c r="C91" s="200" t="s">
         <v>1505</v>
       </c>
       <c r="D91" s="186"/>
@@ -45782,15 +45782,15 @@
       <c r="B92" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C92" s="184"/>
-      <c r="D92" s="175"/>
-      <c r="E92" s="175"/>
-      <c r="F92" s="175"/>
-      <c r="G92" s="175"/>
-      <c r="H92" s="175"/>
-      <c r="I92" s="175"/>
-      <c r="J92" s="175"/>
-      <c r="K92" s="175"/>
+      <c r="C92" s="172"/>
+      <c r="D92" s="173"/>
+      <c r="E92" s="173"/>
+      <c r="F92" s="173"/>
+      <c r="G92" s="173"/>
+      <c r="H92" s="173"/>
+      <c r="I92" s="173"/>
+      <c r="J92" s="173"/>
+      <c r="K92" s="173"/>
       <c r="L92" s="13"/>
     </row>
     <row r="93" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -47632,18 +47632,18 @@
       <c r="B174" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C174" s="182" t="str">
+      <c r="C174" s="174" t="str">
         <f t="array" ref="C174">IF(C175="","?",C175)&amp;IF(C176="","","; downloaded "&amp;C176)&amp;IF(C177="","","; "&amp;C177)</f>
         <v>?; downloaded 2026-05-26</v>
       </c>
-      <c r="D174" s="175"/>
-      <c r="E174" s="175"/>
-      <c r="F174" s="175"/>
-      <c r="G174" s="175"/>
-      <c r="H174" s="175"/>
-      <c r="I174" s="175"/>
-      <c r="J174" s="175"/>
-      <c r="K174" s="175"/>
+      <c r="D174" s="173"/>
+      <c r="E174" s="173"/>
+      <c r="F174" s="173"/>
+      <c r="G174" s="173"/>
+      <c r="H174" s="173"/>
+      <c r="I174" s="173"/>
+      <c r="J174" s="173"/>
+      <c r="K174" s="173"/>
       <c r="L174" s="13"/>
     </row>
     <row r="175" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -47651,15 +47651,15 @@
       <c r="B175" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C175" s="183"/>
-      <c r="D175" s="175"/>
-      <c r="E175" s="175"/>
-      <c r="F175" s="175"/>
-      <c r="G175" s="175"/>
-      <c r="H175" s="175"/>
-      <c r="I175" s="175"/>
-      <c r="J175" s="175"/>
-      <c r="K175" s="175"/>
+      <c r="C175" s="175"/>
+      <c r="D175" s="173"/>
+      <c r="E175" s="173"/>
+      <c r="F175" s="173"/>
+      <c r="G175" s="173"/>
+      <c r="H175" s="173"/>
+      <c r="I175" s="173"/>
+      <c r="J175" s="173"/>
+      <c r="K175" s="173"/>
       <c r="L175" s="13"/>
     </row>
     <row r="176" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -47667,17 +47667,17 @@
       <c r="B176" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C176" s="183" t="s">
+      <c r="C176" s="175" t="s">
         <v>37</v>
       </c>
-      <c r="D176" s="175"/>
-      <c r="E176" s="175"/>
-      <c r="F176" s="175"/>
-      <c r="G176" s="175"/>
-      <c r="H176" s="175"/>
-      <c r="I176" s="175"/>
-      <c r="J176" s="175"/>
-      <c r="K176" s="175"/>
+      <c r="D176" s="173"/>
+      <c r="E176" s="173"/>
+      <c r="F176" s="173"/>
+      <c r="G176" s="173"/>
+      <c r="H176" s="173"/>
+      <c r="I176" s="173"/>
+      <c r="J176" s="173"/>
+      <c r="K176" s="173"/>
       <c r="L176" s="13"/>
     </row>
     <row r="177" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -47701,7 +47701,7 @@
       <c r="B178" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C178" s="201" t="s">
+      <c r="C178" s="200" t="s">
         <v>1508</v>
       </c>
       <c r="D178" s="186"/>
@@ -47719,15 +47719,15 @@
       <c r="B179" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C179" s="184"/>
-      <c r="D179" s="175"/>
-      <c r="E179" s="175"/>
-      <c r="F179" s="175"/>
-      <c r="G179" s="175"/>
-      <c r="H179" s="175"/>
-      <c r="I179" s="175"/>
-      <c r="J179" s="175"/>
-      <c r="K179" s="175"/>
+      <c r="C179" s="172"/>
+      <c r="D179" s="173"/>
+      <c r="E179" s="173"/>
+      <c r="F179" s="173"/>
+      <c r="G179" s="173"/>
+      <c r="H179" s="173"/>
+      <c r="I179" s="173"/>
+      <c r="J179" s="173"/>
+      <c r="K179" s="173"/>
       <c r="L179" s="13"/>
     </row>
     <row r="180" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -47746,12 +47746,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C174:K174"/>
-    <mergeCell ref="C175:K175"/>
-    <mergeCell ref="C176:K176"/>
-    <mergeCell ref="C177:K177"/>
-    <mergeCell ref="C179:K179"/>
-    <mergeCell ref="C178:K178"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="C94:K94"/>
     <mergeCell ref="C87:K87"/>
@@ -47762,6 +47756,12 @@
     <mergeCell ref="C91:K91"/>
     <mergeCell ref="C5:K5"/>
     <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C174:K174"/>
+    <mergeCell ref="C175:K175"/>
+    <mergeCell ref="C176:K176"/>
+    <mergeCell ref="C177:K177"/>
+    <mergeCell ref="C179:K179"/>
+    <mergeCell ref="C178:K178"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
@@ -47786,20 +47786,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="182" t="s">
         <v>1509</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="178"/>
+      <c r="L1" s="178"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="156"/>
@@ -47893,15 +47893,15 @@
       <c r="B5" s="21" t="s">
         <v>1511</v>
       </c>
-      <c r="C5" s="176"/>
-      <c r="D5" s="175"/>
-      <c r="E5" s="175"/>
-      <c r="F5" s="175"/>
-      <c r="G5" s="175"/>
-      <c r="H5" s="175"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="175"/>
-      <c r="K5" s="175"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="173"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="173"/>
+      <c r="H5" s="173"/>
+      <c r="I5" s="173"/>
+      <c r="J5" s="173"/>
+      <c r="K5" s="173"/>
       <c r="L5" s="22"/>
     </row>
     <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -48067,15 +48067,15 @@
       <c r="B13" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="176"/>
-      <c r="D13" s="175"/>
-      <c r="E13" s="175"/>
-      <c r="F13" s="175"/>
-      <c r="G13" s="175"/>
-      <c r="H13" s="175"/>
-      <c r="I13" s="175"/>
-      <c r="J13" s="175"/>
-      <c r="K13" s="175"/>
+      <c r="C13" s="184"/>
+      <c r="D13" s="173"/>
+      <c r="E13" s="173"/>
+      <c r="F13" s="173"/>
+      <c r="G13" s="173"/>
+      <c r="H13" s="173"/>
+      <c r="I13" s="173"/>
+      <c r="J13" s="173"/>
+      <c r="K13" s="173"/>
       <c r="L13" s="22"/>
     </row>
     <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -52581,15 +52581,15 @@
       <c r="B118" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="C118" s="176"/>
-      <c r="D118" s="175"/>
-      <c r="E118" s="175"/>
-      <c r="F118" s="175"/>
-      <c r="G118" s="175"/>
-      <c r="H118" s="175"/>
-      <c r="I118" s="175"/>
-      <c r="J118" s="175"/>
-      <c r="K118" s="175"/>
+      <c r="C118" s="184"/>
+      <c r="D118" s="173"/>
+      <c r="E118" s="173"/>
+      <c r="F118" s="173"/>
+      <c r="G118" s="173"/>
+      <c r="H118" s="173"/>
+      <c r="I118" s="173"/>
+      <c r="J118" s="173"/>
+      <c r="K118" s="173"/>
       <c r="L118" s="22"/>
     </row>
     <row r="119" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -54302,15 +54302,15 @@
       <c r="B160" s="21" t="s">
         <v>402</v>
       </c>
-      <c r="C160" s="176"/>
-      <c r="D160" s="175"/>
-      <c r="E160" s="175"/>
-      <c r="F160" s="175"/>
-      <c r="G160" s="175"/>
-      <c r="H160" s="175"/>
-      <c r="I160" s="175"/>
-      <c r="J160" s="175"/>
-      <c r="K160" s="175"/>
+      <c r="C160" s="184"/>
+      <c r="D160" s="173"/>
+      <c r="E160" s="173"/>
+      <c r="F160" s="173"/>
+      <c r="G160" s="173"/>
+      <c r="H160" s="173"/>
+      <c r="I160" s="173"/>
+      <c r="J160" s="173"/>
+      <c r="K160" s="173"/>
       <c r="L160" s="22"/>
     </row>
     <row r="161" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -58796,15 +58796,15 @@
       <c r="B264" s="21" t="s">
         <v>610</v>
       </c>
-      <c r="C264" s="176"/>
-      <c r="D264" s="175"/>
-      <c r="E264" s="175"/>
-      <c r="F264" s="175"/>
-      <c r="G264" s="175"/>
-      <c r="H264" s="175"/>
-      <c r="I264" s="175"/>
-      <c r="J264" s="175"/>
-      <c r="K264" s="175"/>
+      <c r="C264" s="184"/>
+      <c r="D264" s="173"/>
+      <c r="E264" s="173"/>
+      <c r="F264" s="173"/>
+      <c r="G264" s="173"/>
+      <c r="H264" s="173"/>
+      <c r="I264" s="173"/>
+      <c r="J264" s="173"/>
+      <c r="K264" s="173"/>
       <c r="L264" s="22"/>
     </row>
     <row r="265" spans="1:12" ht="20.100000000000001" customHeight="1">
